--- a/Docs/JSON/SPOD_FIELD_REGISTRY.xlsx
+++ b/Docs/JSON/SPOD_FIELD_REGISTRY.xlsx
@@ -5519,7 +5519,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ограничения выборки операций по атрибутам источника для расчёта индикатора; в UI действует каскад: INDICATOR_CODE → code → type/match → condition|dt|value.</t>
+          <t>Ограничения выборки операций по атрибутам источника для расчёта индикатора; каскад в UI: INDICATOR_CODE → code → type/match → condition|dt|value. Источник справочника: dm_gamification_filteredattribute_dic.xlsx.</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Массив значений для текстовых условий; при наличии непустых condition_options в каталоге действует whitelist допустимых значений.</t>
+          <t>Массив значений для строковых условий; список допустимых значений берётся из condition_options (источник: dm_gamification_filteredattribute_dic.xlsx), в UI используется whitelist + datalist.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>required=False; allows_empty=True; dynamic_by=...+filtered_attribute_type; whitelist_from=condition_options</t>
+          <t>required=False; allows_empty=True; dynamic_by=...+filtered_attribute_type; whitelist_from=condition_options; datalist=yes</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Дата для условий по датам (YYYY-MM-DD); при наличии в каталоге применяются границы filtered_attribute_min_date/max_date.</t>
+          <t>Дата для условий по датам; при типах DATE/DATETIME/TIMESTAMP ввод в UI через datepicker, сохранение в ключ filtered_attribute_dt.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>required=False; allows_empty=True; min/max from indicator_filter_catalog.by_type</t>
+          <t>required=False; allows_empty=True; input=date_picker; min/max from indicator_filter_catalog.by_type</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Значение для числового условия фильтра; при наличии в каталоге применяются границы filtered_attribute_min_value/max_value.</t>
+          <t>Значение для числового условия фильтра; используется для INTEGER/DECIMAL, границы берутся из каталога min/max.</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>required=False; allows_empty=True; min/max from indicator_filter_catalog.by_type</t>
+          <t>required=False; allows_empty=True; input=numeric; min/max from indicator_filter_catalog.by_type</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
